--- a/upload_file/products_to_import.xlsx
+++ b/upload_file/products_to_import.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\home\Desktop\phoneshop-night\upload_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C6BB65-93DA-45BA-941A-E1E906E80C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB46A457-BEDB-4597-8567-F0C9CF4C66CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8BB824D1-22C5-41A6-9B5C-0A5D0B664E27}"/>
   </bookViews>
@@ -54,7 +54,7 @@
     <t>NO</t>
   </si>
   <si>
-    <t>30/02/20243</t>
+    <t>2024-09-16</t>
   </si>
 </sst>
 </file>
@@ -62,7 +62,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -93,9 +93,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,77 +450,23 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="E2">
-        <v>20</v>
-      </c>
-      <c r="F2" s="1">
-        <f ca="1">TODAY()</f>
-        <v>45519</v>
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>120</v>
-      </c>
-      <c r="E3">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1">
-        <f t="shared" ref="F3:F5" ca="1" si="0">TODAY()</f>
-        <v>45519</v>
-      </c>
+      <c r="F3" s="1"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>130</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>45519</v>
-      </c>
+      <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>140</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="F5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/upload_file/products_to_import.xlsx
+++ b/upload_file/products_to_import.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\home\Desktop\phoneshop-night\upload_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB46A457-BEDB-4597-8567-F0C9CF4C66CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA36E18B-0734-4B70-A3CA-972F78FBDB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8BB824D1-22C5-41A6-9B5C-0A5D0B664E27}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="21600" windowHeight="11295" xr2:uid="{8BB824D1-22C5-41A6-9B5C-0A5D0B664E27}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Model Id</t>
   </si>
@@ -51,10 +51,7 @@
     <t>Import Date</t>
   </si>
   <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>2024-09-16</t>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -62,7 +59,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-409]m/d/yy\ h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="168" formatCode="yyyy/mm/dd\ h:mm;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -93,10 +90,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -411,12 +407,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DC38A97-53CD-4640-B381-5638943BE596}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="5" width="20.85546875" customWidth="1"/>
     <col min="6" max="6" width="31.28515625" customWidth="1"/>
-    <col min="7" max="7" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -450,23 +445,36 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>350</v>
+        <v>1500</v>
       </c>
       <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
+        <v>10000</v>
+      </c>
+      <c r="F2" s="1">
+        <f ca="1">NOW()</f>
+        <v>45520.633953124998</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F5" s="1"/>
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+      <c r="F3" s="1">
+        <f ca="1">NOW()</f>
+        <v>45520.633953124998</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
